--- a/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
+++ b/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">БЮДЖЕТ МЕРОПРИЯТИЯ</t>
   </si>
   <si>
-    <t xml:space="preserve">Оркестр, концерт · 20.10.2026 · Музей ЗИЛАРТ, бул. Братьев Весниных, 3 (3 этаж)</t>
+    <t xml:space="preserve">Концерт · 20.10.2026 · Музей ЗИЛАРТ</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Технический райдер (смета СМ-2026-024)</t>
   </si>
   <si>
-    <t xml:space="preserve">Спотыкач, 04.10.2026: позиции 68 790 ₽ + налог 10%</t>
+    <t xml:space="preserve">Округлённая сумма. По смете Спотыкача 75 669 ₽ (68 790 ₽ + налог 10%)</t>
   </si>
   <si>
     <t xml:space="preserve">Музыканты</t>
@@ -61,10 +61,10 @@
     <t xml:space="preserve">ИТОГО РАСХОДЫ</t>
   </si>
   <si>
-    <t xml:space="preserve">Комиссия сверху</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Начисляется на всю сумму расходов</t>
+    <t xml:space="preserve">Комиссия и налоги</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% на всю сумму расходов</t>
   </si>
   <si>
     <t xml:space="preserve">ИТОГО К ОПЛАТЕ</t>
@@ -73,10 +73,10 @@
     <t xml:space="preserve">• Жёлтые ячейки — вводимые значения, остальное считается формулами.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Райдер взят итоговой суммой по смете СМ-2026-024 (налог 10% уже внутри).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Комиссия округлена до рубля: точное значение 35 133,80 ₽.</t>
+    <t xml:space="preserve">• Райдер округлён до 90 000 ₽; по смете СМ-2026-024 выходит 75 669 ₽ (налог 10% внутри).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Комиссия и налоги — 20% на всю сумму расходов.</t>
   </si>
   <si>
     <t xml:space="preserve">• Дата на уточнении — по примечанию в смете ожидается согласование с артистами после просмотра площадки.</t>
@@ -595,11 +595,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>75669</v>
+        <v>90000</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">C5*D5</f>
-        <v>75669</v>
+        <v>90000</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>8</v>
@@ -653,7 +653,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="12" t="n">
         <f aca="false">SUM(E5:E7)</f>
-        <v>175669</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -668,7 +668,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">ROUND($E$8*D9,0)</f>
-        <v>35134</v>
+        <v>38000</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -683,7 +683,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="16" t="n">
         <f aca="false">E8+E9</f>
-        <v>210803</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
+++ b/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Сумма, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">Технический райдер (смета СМ-2026-024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Округлённая сумма. По смете Спотыкача 75 669 ₽ (68 790 ₽ + налог 10%)</t>
+    <t xml:space="preserve">Технический райдер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По скорректированному райдеру</t>
   </si>
   <si>
     <t xml:space="preserve">Музыканты</t>

--- a/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
+++ b/event-zilart/Бюджет_ЗИЛАРТ_20.10.2026.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Технический райдер</t>
   </si>
   <si>
-    <t xml:space="preserve">По скорректированному райдеру</t>
+    <t xml:space="preserve">Смета СМ-2026-024, ред. от 05.10.2026: 72 305 ₽ + налог 10%</t>
   </si>
   <si>
     <t xml:space="preserve">Музыканты</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">• Жёлтые ячейки — вводимые значения, остальное считается формулами.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Райдер округлён до 90 000 ₽; по смете СМ-2026-024 выходит 75 669 ₽ (налог 10% внутри).</t>
+    <t xml:space="preserve">• Райдер — итог сметы СМ-2026-024 в редакции от 05.10.2026 (налог 10% внутри).</t>
   </si>
   <si>
     <t xml:space="preserve">• Комиссия и налоги — 20% на всю сумму расходов.</t>
@@ -595,11 +595,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>90000</v>
+        <v>79536</v>
       </c>
       <c r="E5" s="9" t="n">
         <f aca="false">C5*D5</f>
-        <v>90000</v>
+        <v>79536</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>8</v>
@@ -653,7 +653,7 @@
       <c r="D8" s="10"/>
       <c r="E8" s="12" t="n">
         <f aca="false">SUM(E5:E7)</f>
-        <v>190000</v>
+        <v>179536</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -668,7 +668,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">ROUND($E$8*D9,0)</f>
-        <v>38000</v>
+        <v>35907</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -683,7 +683,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="16" t="n">
         <f aca="false">E8+E9</f>
-        <v>228000</v>
+        <v>215443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
